--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0057.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0057.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Tò Mò</t>
+          <t>Người đàn ông tò mò</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Tiếp tục Exploration</t>
+          <t>Tiếp tục khám phá</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Khúc Bi Ca Của Kẻ Sa Ngã: Chronorift Yakujin</t>
+          <t>Khúc Bi Ca Sa Ngã: Yakujin Vực Thời Gian</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>"Thuyền Trưởng Già" Davide</t>
+          <t>"Đại úy" Davide</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Light Sensitive Component</t>
+          <t>Thành Phần Nhạy Quang</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Kính màu ở giữa</t>
+          <t>Phần Giữa Kính Màu</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Obelisk</t>
+          <t>Đài Kỷ Niệm</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Memo</t>
+          <t>Ghi chú</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Lemongrass</t>
+          <t>Sả Dại</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Tacetite Bloom</t>
+          <t>Nở Hoa Tacetite</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Male Stranger</t>
+          <t>Người lạ mặt</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Đóng cổng kết nối</t>
+          <t>Đóng cánh cổng</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Straightforward Courier</t>
+          <t>Người đưa tin thẳng thắn</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>: Limbo Rondo</t>
+          <t>: Rondo Limbo</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Giấc Mơ Ngôi Sao</t>
+          <t>Giấc Mộng Vì Sao</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Train Lover</t>
+          <t>Tình Yêu Chiến Binh</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Mechanical Variable Weapon</t>
+          <t>Vũ Khí Cơ Giới Đa Năng</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Jinyue</t>
+          <t>Kim Nguyệt</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Ol' Climber</t>
+          <t>Lão leo núi</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Thông Báo Mẫu Thí Nghiệm Bị Mất</t>
+          <t>Thông Báo về Mất Mẫu Thí Nghiệm</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Mời bạn đồng hành thưởng thức âm nhạc</t>
+          <t>Mời bạn bè cùng thưởng thức âm nhạc</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Hai</t>
+          <t>Hừm</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Tambourine Duo</t>
+          <t>Bộ Đôi Tambourine</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tham gia "Thử Thách Rèn Luyện"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Standing Mannequin</t>
+          <t>Bộ khung người đứng trước mặt</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Feed</t>
+          <t>Cho ăn</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Voidspawn: Frostbite Coleoid</t>
+          <t>Voidspawn: Coleoid Băng Giá</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Nghỉ ngơi một chút</t>
+          <t>Nghỉ ngơi đi</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Cetus the Tidebreaker</t>
+          <t>Cetus Kẻ Phá Thủy Triều</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Nightmare Kelpie</t>
+          <t>Ngựa Kelpie Ác Mộng</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Lady</t>
+          <t>Tiểu thư</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Phantom: Reminiscence Kronaclaw</t>
+          <t>Hồn Ma: Hồi Ức Kronaclaw</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Kiểm tra bức tranh tường lớn</t>
+          <t>Kiểm tra bức tranh tường lớn kia</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>A Boy's Notebook</t>
+          <t>Cuốn Sổ Của Một Cậu Bé</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Stammering Pirate</t>
+          <t>Cướp Biển Lắp Bắp</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Wenmao</t>
+          <t>Văn Mão</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Mingming</t>
+          <t>Minh Minh</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Pilgrim's Shell</t>
+          <t>Vỏ Sò Hành Hương</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Priest Alessio</t>
+          <t>Linh mục Alessio</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Luoluo</t>
+          <t>Lộ Lộ</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Fruit Crackle</t>
+          <t>Tiếng Nổ Trái Cây</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>[Lollo Campaign] Overview</t>
+          <t>["Chiến dịch Lollo] Tổng quan"</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>Dạ...</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Hồ Sơ Nghiên Cứu Của Dollmaker</t>
+          <t>Hồ sơ Nghiên cứu của Dollmaker</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Sử dụng Thiết bị Truyền Khối Lượng</t>
+          <t>Kích hoạt Thiết Bị Truyền Khối Lượng</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Switch Channel</t>
+          <t>Chuyển kênh</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Touch</t>
+          <t>Chạm</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Jinlan</t>
+          <t>Kim Lan</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Frost</t>
+          <t>Băng giá</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Cheerful Duelist</t>
+          <t>Duelist Vui Vẻ</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Dark: Rocksteady Guardian</t>
+          <t>Hắc: Rocksteady Guardian</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Gray Ear the Rabbit</t>
+          <t>Thỏ Xám Tai Xám</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Cậu Bé U Sầu</t>
+          <t>Chàng Trai Đau Khổ</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>"Expressway Bulletin"</t>
+          <t>"Thông Báo Đường Cao Tốc"</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Destructible Boulder</t>
+          <t>Tảng Đá Có Thể Phá Hủy</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Tremor Warrior</t>
+          <t>Chiến Binh Rung Chấn</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Phantom: Fallacy of Không Return</t>
+          <t>Phantom: Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>(Giữ) Chuyển sang màn tiếp theo</t>
+          <t>(Giữ) Bước vào chương tiếp theo</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Samousas</t>
+          <t>Bánh samosa</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Hộp máy ảnh</t>
+          <t>Khung máy quay</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Bia mộ thấm đẫm mệt mỏi</t>
+          <t>Ngôi mộ thấm đẫm vẻ mệt mỏi</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Exile Lookout</t>
+          <t>Lưu Đày Canh Gác</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Xuanxuan</t>
+          <t>Huyền Huyền</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Lắng nghe Echo</t>
+          <t>Hãy lắng nghe những tiếng vọng</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Scatter Prism</t>
+          <t>Lăng Kính Phân Tán</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Play Channel 3</t>
+          <t>Phát Kênh 3</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Chop Chop: Rightless</t>
+          <t>Chop Chop: Không Tay Phải</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>"Minghu"</t>
+          <t>"Minh Hồ"</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Questless Knight</t>
+          <t>Hiệp Sĩ Không Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Space Station Chest</t>
+          <t>Rương Trạm Vũ Trụ</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Học sinh Lo Lắng</t>
+          <t>Học Sinh Lo Lắng</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Havoc Warrior</t>
+          <t>Chiến Binh Hỗn Loạn</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Tidal Blight Trace</t>
+          <t>Dấu Vết Ô Uế Thủy Triều</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Gift Vendor Mammon</t>
+          <t>Mammon - Người bán quà</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Heying</t>
+          <t>Hừm...</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Bộ Kích Hoạt Sương Mù Truyền Tải Bờ Biển Đen (Nhỏ)</t>
+          <t>Bộ Kích Hoạt Truyền Tin Sương Mù Bờ Biển Đen (Cỡ Nhỏ)</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Tìm chiếc mũ tròn</t>
+          <t>Tìm kiếm chiếc mũ tròn</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Học sinh Tỉ Mỉ</t>
+          <t>Học Sinh Tỉ Mỉ</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Cô Gái Bướng Bỉnh</t>
+          <t>Cô nàng bướng bỉnh</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Đợi ở đây</t>
+          <t>Đợi ở đây.</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Nightmare: Tempest Mephis</t>
+          <t>Ác Mộng: Tempest Mephis</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Changli Cube</t>
+          <t>Khối Changli</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Eveflitter</t>
+          <t>Bươm Bướm Đêm</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Kích hoạt thang máy</t>
+          <t>Kích hoạt thang máy.</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Bei Ji</t>
+          <t>Bắc Cơ</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Strange Cargo</t>
+          <t>Hàng Hóa Khó Hiểu</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Jinghua</t>
+          <t>Cảnh Hoa</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Nhà Nghiên cứu Trông Mệt Mỏi</t>
+          <t>Nhà Nghiên Cứu Trông Mệt Mỏi</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Transporter</t>
+          <t>Thiết bị vận chuyển</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Tiến tới Trận Chiến Cuối</t>
+          <t>Tiến vào Trận Chiến Cuối Cùng</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Nhân viên Hỗ trợ Cao cấp</t>
+          <t>Nhân Viên Hậu Cần Cao Cấp</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Ông già</t>
+          <t>Lão Già</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Ngồi quan sát</t>
+          <t>Ngồi quan sát đi</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Stringless Lunachord</t>
+          <t>Lunachord Vô Âm</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Frightened Exile</t>
+          <t>Người lưu đày hoảng loạn</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Morri Cow</t>
+          <t>Bò Morri</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Vacationer Namipon</t>
+          <t>Du khách Namipon</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Chờ tàu đến</t>
+          <t>Hãy chờ tàu đến.</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Diurnus Knight</t>
+          <t>Hiệp Sĩ Diurnus</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Craft</t>
+          <t>Chế Tạo</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Sweet Tooth Namipon</t>
+          <t>Namipon Háu Ăn Ngọt</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Ji Liubai</t>
+          <t>Cơ Lục Bách</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Wunian</t>
+          <t>Ngũ Niên</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Shaper</t>
+          <t>Người Hóa Thân</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Đi nghỉ ngơi</t>
+          <t>Đi nghỉ ngơi đi.</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>:"Gánh nặng của Trí tuệ"</t>
+          <t>: "Gánh Nặng Trí Tuệ"</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu bất an</t>
+          <t>Nhà Nghiên Cứu Đáng Ngờ</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Historian</t>
+          <t>Nhà Sử Học</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Spacetrek Convoy Transport Report</t>
+          <t>Báo cáo Vận chuyển Đoàn vận tải Spacetrek</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tín đồ canh gác</t>
+          <t>Tín Đồ Canh Gác</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Mural</t>
+          <t>Bích họa</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Fuling</t>
+          <t>Phúc Linh</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Không tìm thấy gì</t>
+          <t>Không tìm thấy gì cả.</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Kiểm tra bảng thông tin</t>
+          <t>Xem bảng thông tin</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Sử dụng lõi năng lượng từ Thiết bị Truyền khối</t>
+          <t>Dùng lõi năng lượng từ Thiết bị Truyền Khối</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Steadfast Midnight Ranger</t>
+          <t>Kỵ Sĩ Bóng Đêm Kiên Cường</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Resonator Nâng cấp</t>
+          <t>Nâng Cấp Resonator</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Trụ đá</t>
+          <t>cột đá</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Exoswarm bị đóng băng</t>
+          <t>Exoswarm bị đóng băng trong băng</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Phantom: Diggy Duggy</t>
+          <t>Bóng Ma: Đào Bới</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu Overdash</t>
+          <t>Nhà nghiên cứu Bay vượt tốc</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Firework</t>
+          <t>Pháo hoa</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Ký ức Endgame</t>
+          <t>Ký Ức Chung Kết</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Bản nhạc số 1</t>
+          <t>Bản Nhạc 1</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Cách chiến đấu Kerasaurs IX</t>
+          <t>Cách chiến đấu với Kerasaurs IX</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Front Desk Attendant</t>
+          <t>Nhân viên lễ tân</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Kiếm của Kẻ hèn nhát</t>
+          <t>Sword of Cowardice</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Kiểm tra giấy tờ</t>
+          <t>Xem mấy tờ giấy này</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Wutheride Transmitter_Group</t>
+          <t>Nhóm Trạm Trung Chuyển Vực Gió</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Jungle Wars Standings</t>
+          <t>Bảng xếp hạng Chiến tranh Rừng xanh</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>: "Nostalgic Filter"</t>
+          <t>: "Bộ Lọc Hoài Niệm"</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Aero Predator</t>
+          <t>Thú Dữ Gió</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Tuner - Actor 1</t>
+          <t>Điều Chỉnh Giả - Diễn Viên 1</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Về bản thân bạn</t>
+          <t>Về bản thân ta</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>: Vanishing Blue</t>
+          <t>: Xanh Biến Mất</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Explosive Spear: Heel</t>
+          <t>Thương Nổ: Mũi Giày</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Thực tập sinh</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>True Crownless: Cycling Scythe</t>
+          <t>Vô Địch Chân Chính: Lưỡi Hái Luân Chuyển</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Elevator</t>
+          <t>Thang Máy</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Gate Keeper</t>
+          <t>Người Gác Cổng</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Nhân viên Đoàn múa Lân Nghiêm túc</t>
+          <t>Nhân Viên Đoàn Múa Lân Nghiêm Túc</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Tường Gió</t>
+          <t>Bức Tường Gió</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Hiệp sĩ của Sự tàn bạo</t>
+          <t>Hiệp Sĩ Tàn Ác</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>The Lifer's Game</t>
+          <t>Trò Chơi Của Kẻ Tù Đày</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Feed</t>
+          <t>Cho ăn</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Red Feather Butterfly</t>
+          <t>Bướm Đỏ Lông Vũ</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Người phụ nữ đang mong đợi</t>
+          <t>Người Phụ Nữ Mang Thai</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Bia mộ lấp lánh ánh sáng ngọc yếu ớt</t>
+          <t>Ngôi mộ lung linh ánh sáng ngọc quý</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Vào Tháp Nghịch Cảnh</t>
+          <t>Bước vào Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Mephis: Sky Piercer</t>
+          <t>Mephis: Xuyên Trời</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Về Thước Đo Quá Khứ</t>
+          <t>Về *Scale of Past*</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Yellowed Newspaper</t>
+          <t>Báo Cũ Phai Màu</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Xinping</t>
+          <t>Tân Bình</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Qingzhou</t>
+          <t>Thanh Châu</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Quý Cô Dịu Dàng</t>
+          <t>Người phụ nữ dịu dàng</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Enable Force Settlement</t>
+          <t>Bật Buộc Kết Toán</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Neon Interaction Point</t>
+          <t>Điểm Tương Tác Neon</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Khu vực chưa xác định</t>
+          <t>Khu Vực Không Xác Định</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Tham gia "Thử Thách Rèn Luyện"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Zhixiu</t>
+          <t>Chí Tú</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Mechascout</t>
+          <t>Tuần Thám Cơ Khí</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Hsin's Fortuity</t>
+          <t>May mắn của Hsin</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Artificial Moon</t>
+          <t>Mặt Trăng Nhân Tạo</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Người Bảo Vệ Thủy Triều Bóng Tối</t>
+          <t>Người Bảo Vệ Thủy Triều Hắc Ám</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>"Haunting Ghost"</t>
+          <t>"Hồn Ma Ám Ảnh"</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Dismiss Little Namipons</t>
+          <t>Thu hồi Namipon Nhỏ</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Sức Mạnh</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Ice Chrysalises</t>
+          <t>Băng Chrysalis</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Wish Bottle</t>
+          <t>Bình Ước Nguyện</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Exam Zone 4</t>
+          <t>Khu Vực Thi 4</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Mutant Organism: Cruisewing</t>
+          <t>Sinh vật thể đột biến: Cruisewing</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Tần số Waystone</t>
+          <t>Tần số Đá Dẫn Đường</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Character Advancement</t>
+          <t>Thăng Tiến Nhân Vật</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Xiaoxuan</t>
+          <t>Tiểu Huyền</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Earnest Duelist</t>
+          <t>Kẻ Đấu Tay Đôi Chân Thành</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Passing Shepherd</t>
+          <t>Mục Đồng Đi Qua</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Ba Lô Người Đưa Thư</t>
+          <t>Ba lô Người đưa tin</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Space Station Jar</t>
+          <t>Bình Trạm Vũ Trụ</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Huanglong Female Official</t>
+          <t>Nữ Quan Bộ Huanglong</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Nâng cột xoắn ốc</t>
+          <t>Dựng cột xoắn ốc lên.</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Fanatic Shark Grunt</t>
+          <t>Lính Cá Mập Cuồng Tín</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Teahouse</t>
+          <t>Quán Trà</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Zani Cube</t>
+          <t>Khối Zani</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Bulletin</t>
+          <t>Bản tin</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Xem sổ phác thảo</t>
+          <t>Kiểm tra cuốn sổ phác thảo</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Silverstein</t>
+          <t>Thạch Băng</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Vault Security</t>
+          <t>An Ninh Kho Tàng</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Lingyan</t>
+          <t>Linh Nghiên</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Yuanwu God</t>
+          <t>Thần Quyền Yuanwu</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Lian Xiaosheng</t>
+          <t>Liên Tiểu Sinh</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Aged Gladiator</t>
+          <t>Đấu Sĩ Lão Luyện</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Swim, Gulpuff, Swim</t>
+          <t>Bơi đi, Gulpuff, bơi lên!</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Xunjing</t>
+          <t>Tuấn Kính</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Deliver Prism Fruit</t>
+          <t>Giao Quả Lăng Kính</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Xiaoran</t>
+          <t>Tiểu Nhiễm</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Lấy quyền điều khiển</t>
+          <t>Lấy lại quyền kiểm soát</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Reader A</t>
+          <t>Người Đọc A</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Old Fisherman</t>
+          <t>Lão Ngư Dân</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tutorial 2 - Dismount Attack</t>
+          <t>Hướng Dẫn 2 - Tấn Công Khi Xuống Xe</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Nightmare: Tick Tack</t>
+          <t>Ác Mộng: Tick Tack</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Mingzhi</t>
+          <t>Minh Chí</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Người Phụ Nữ Tức Giận</t>
+          <t>Người phụ nữ nổi giận</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Cô Gái Nói Linh Tinh</t>
+          <t>Cô Gái Lang Thang</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Mức Danh Vọng Đề Xuất: 201-300</t>
+          <t>Cấp Độ Vinh Quang Đề Xuất: 201-300</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Photon Barrier Lock - Group</t>
+          <t>Khóa Chắn Photon - Nhóm</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Sea Bunny</t>
+          <t>Thỏ Biển</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Conti</t>
+          <t>Con...</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Strange Exile</t>
+          <t>Kẻ Lưu Đày Bí Ẩn</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Anomaly: Feilian Beringal</t>
+          <t>Dị thường: Feilian Beringal</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Chàng Trai Cau Có</t>
+          <t>Chàng Trai Cau Mày</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Xoay bức tượng</t>
+          <t>Xoay bức tượng.</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Khu Vực Thử Thách IV</t>
+          <t>Khu vực thử thách IV</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Quan sát trong im lặng</t>
+          <t>Lặng lẽ quan sát</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Echo Broker</t>
+          <t>Người Môi Giới Echo</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Dark Tide Cocoon</t>
+          <t>Kén Thủy Triều Bóng Tối</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Quan sát ảo ảnh</t>
+          <t>Hãy quan sát những ảo ảnh</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Hocus Pocus</t>
+          <t>Ảo thuật biến!</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Flora Reindeer</t>
+          <t>Tuần Lộc Flora</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Kiểm tra hộp giấy</t>
+          <t>Kiểm tra cái hộp giấy</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Hỏi về tình hình</t>
+          <t>Hỏi tình hình hiện tại.</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Switch Echoes</t>
+          <t>Chuyển Echo</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>Lắng nghe</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Tôi sẽ lấy một cái</t>
+          <t>Ta sẽ lấy một cái.</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Terraspawn Fungus</t>
+          <t>Nấm Terraspawn</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Medic</t>
+          <t>Hộ lý</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Xâm nhập Bộ Truyền Thanh</t>
+          <t>Xâm nhập Hệ Thống Thông Báo</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Hào Hứng</t>
+          <t>Nhà nghiên cứu hứng thú</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Timid Soliskin</t>
+          <t>Người Da Mặt Trời Nhút Nhát</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Liondance Troupe Lilili</t>
+          <t>Lân Vũ là một phong cách múa bắt nguồn từ võ thuật. Các tư thế và bộ chân thường lấy cảm hứng từ võ thuật truyền thống của Hoàng Long, trong đó cú lộn người về sau là động tác cơ bản không thể thiếu.</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Twin Nova: Void Revenant</t>
+          <t>Song Tinh: Hồn Ma Hư Không</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Bắt Đầu Neo Từ Đầu</t>
+          <t>Bắt đầu Neo giữ từ đầu</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Lianke</t>
+          <t>Liên Khả</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Giáo Sư Karl</t>
+          <t>Giáo sư Karl</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Hermit Owl</t>
+          <t>Cú Ẩn Dật</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Jiahui</t>
+          <t>Gia Huy</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>"Grave Anathema"</t>
+          <t>"Ác Nghiệt U Minh"</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Changfeng</t>
+          <t>Xương Phong</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Bia Mộ Thì Thầm Một Bản Ballad Du Dương</t>
+          <t>Ngôi mộ thì thầm khúc ballad du dương</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Mảnh Kính Nhuộm Màu</t>
+          <t>Mảnh Kính Màu</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Quay lại điểm xuất phát</t>
+          <t>Quay về điểm xuất phát</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Kết Nối Với Sonodisk: Jue</t>
+          <t>Kết nối với Sonodisk: Jue</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Grapple Sonance Casket</t>
+          <t>Hòm Sonance Móc</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Elevator</t>
+          <t>Thang Máy</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>Lắng nghe</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Đến Hầm Ngầm Kho Tàng</t>
+          <t>Đến Hầm Ngầm Vault</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Ichor Container</t>
+          <t>Bình Chứa Dịch Huyết</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Ngồi đợi</t>
+          <t>Ngồi xuống đợi đi</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>The False Sovereign</t>
+          <t>Kẻ Quân Vương Giả Mạo</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Thương nhân giàu có</t>
+          <t>Thương Nhân Giàu Có</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Ceremonial Officer Bruno</t>
+          <t>Quan Viên Nghi Lễ Bruno</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Stig</t>
+          <t>Vết Nhơ</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Quay lại gặp Honami</t>
+          <t>Trở lại gặp Honami</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Chuối</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Qinghe</t>
+          <t>Thanh Hà</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Kronablight</t>
+          <t>Kẻ Ám Sương</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Qinglan</t>
+          <t>Thanh Lan</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Passing Roya</t>
+          <t>Roya Đi Qua</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Floating Tacetite</t>
+          <t>Tacetite trôi nổi</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Variable Manager</t>
+          <t>Quản Lý Biến Số</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Gói phụ tùng</t>
+          <t>Gói linh kiện</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Điều tra ghi chú</t>
+          <t>Xem qua những tờ ghi chú</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Generic Dorm Door Status Log</t>
+          <t>Nhật Ký Trạng Thái Cửa Ký Túc Chung</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Pray</t>
+          <t>Cầu nguyện</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Học sinh Royan</t>
+          <t>Học Giả Royan</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Suspicious Spectator</t>
+          <t>Khán Giả Đáng Ngờ</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Tham gia "Thử thách Giả mạo"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>Trống rỗng</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Universal Training Automaton Assembly: Loại trạng thái</t>
+          <t>Lắp Ráp Máy Huấn Luyện Chung: Loại Trạng Thái</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>KU-Roro the Welder</t>
+          <t>Lanxiang Desert Outskirts</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Tôi muốn mua một ít thức ăn</t>
+          <t>Tao muốn mua chút đồ ăn</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Thành viên Fisalia chán nản</t>
+          <t>Thành Viên Fisalia Tuyệt Vọng</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Lối chơi mechanic placeholder</t>
+          <t>Chỗ giữ chỗ cơ chế gameplay</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Qingling</t>
+          <t>Thanh Linh</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
